--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251029_201755.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251029_201755.xlsx
@@ -3754,7 +3754,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251029_201755.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251029_201755.xlsx
@@ -3754,7 +3754,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251029_201755.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251029_201755.xlsx
@@ -4798,7 +4798,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251029_201755.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251029_201755.xlsx
@@ -4856,7 +4856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251029_201755.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251029_201755.xlsx
@@ -4798,7 +4798,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251029_201755.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251029_201755.xlsx
@@ -4798,7 +4798,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251029_201755.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251029_201755.xlsx
@@ -4798,7 +4798,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251029_201755.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251029_201755.xlsx
@@ -3754,7 +3754,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251029_201755.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251029_201755.xlsx
@@ -3754,7 +3754,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251029_201755.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251029_201755.xlsx
@@ -4856,7 +4856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251029_201755.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251029_201755.xlsx
@@ -3754,7 +3754,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251029_201755.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251029_201755.xlsx
@@ -3754,7 +3754,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251029_201755.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251029_201755.xlsx
@@ -4798,7 +4798,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251029_201755.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251029_201755.xlsx
@@ -3754,7 +3754,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
